--- a/download/Urdu_NLP_Research_Survey.xlsx
+++ b/download/Urdu_NLP_Research_Survey.xlsx
@@ -12,11 +12,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Task Coverage" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Dataset Catalog" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Gap Analysis" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Feasibility &amp; ROI" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. All Papers'!$A$3:$N$253</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3. Task Coverage'!$A$5:$G$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'4. Dataset Catalog'!$A$5:$K$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'6. Feasibility &amp; ROI'!$A$11:$P$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="48">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -225,6 +227,85 @@
       <color rgb="002E7D32"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00333333"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FB8C00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009E9E9E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00ED6C02"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C62828"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="002E7D32"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -264,7 +345,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -300,11 +381,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="001F4E79"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -472,6 +603,99 @@
     <xf numFmtId="0" fontId="33" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1083,7 +1307,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>Headline Statistics</t>
         </is>
@@ -31516,4 +31740,3916 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Feasibility &amp; ROI Analysis — Which Gaps Are Easy Wins for Reputable Journals?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="43" t="inlineStr">
+        <is>
+          <t>Methodology: ROI score = (Impact × Publication Potential) ÷ (Effort × Compute × Labeling cost). Higher ROI = bigger bang for buck. Sorted by ROI descending — top entries are your easiest paths to Q1/CCF-A publications. Look for entries tagged 'top 5 easy win' — these are low effort, high impact, minimal annotation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="60" t="inlineStr">
+        <is>
+          <t>ROI Score Interpretation:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="61" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B6" s="62" t="inlineStr">
+        <is>
+          <t>EASY WIN — low effort, high impact, minimal/no annotation. Submit to Q1/CCF-A in 4-10 weeks.</t>
+        </is>
+      </c>
+      <c r="C6" s="63" t="n"/>
+      <c r="D6" s="63" t="n"/>
+      <c r="E6" s="63" t="n"/>
+      <c r="F6" s="63" t="n"/>
+      <c r="G6" s="63" t="n"/>
+      <c r="H6" s="63" t="n"/>
+      <c r="I6" s="63" t="n"/>
+      <c r="J6" s="63" t="n"/>
+      <c r="K6" s="63" t="n"/>
+      <c r="L6" s="63" t="n"/>
+      <c r="M6" s="63" t="n"/>
+      <c r="N6" s="63" t="n"/>
+      <c r="O6" s="63" t="n"/>
+      <c r="P6" s="64" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="61" t="inlineStr">
+        <is>
+          <t>7-8</t>
+        </is>
+      </c>
+      <c r="B7" s="62" t="inlineStr">
+        <is>
+          <t>GOOD OPPORTUNITY — moderate effort, decent impact. Submit to Q1/CCF-A in 8-16 weeks.</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="n"/>
+      <c r="D7" s="63" t="n"/>
+      <c r="E7" s="63" t="n"/>
+      <c r="F7" s="63" t="n"/>
+      <c r="G7" s="63" t="n"/>
+      <c r="H7" s="63" t="n"/>
+      <c r="I7" s="63" t="n"/>
+      <c r="J7" s="63" t="n"/>
+      <c r="K7" s="63" t="n"/>
+      <c r="L7" s="63" t="n"/>
+      <c r="M7" s="63" t="n"/>
+      <c r="N7" s="63" t="n"/>
+      <c r="O7" s="63" t="n"/>
+      <c r="P7" s="64" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="65" t="inlineStr">
+        <is>
+          <t>5-6</t>
+        </is>
+      </c>
+      <c r="B8" s="66" t="inlineStr">
+        <is>
+          <t>BIG PROJECT — high effort but big publication. Submit to top venue in 16-30 weeks.</t>
+        </is>
+      </c>
+      <c r="C8" s="63" t="n"/>
+      <c r="D8" s="63" t="n"/>
+      <c r="E8" s="63" t="n"/>
+      <c r="F8" s="63" t="n"/>
+      <c r="G8" s="63" t="n"/>
+      <c r="H8" s="63" t="n"/>
+      <c r="I8" s="63" t="n"/>
+      <c r="J8" s="63" t="n"/>
+      <c r="K8" s="63" t="n"/>
+      <c r="L8" s="63" t="n"/>
+      <c r="M8" s="63" t="n"/>
+      <c r="N8" s="63" t="n"/>
+      <c r="O8" s="63" t="n"/>
+      <c r="P8" s="64" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="B9" s="68" t="inlineStr">
+        <is>
+          <t>MAJOR UNDERTAKING — needs team + compute budget + domain experts. 6-12 month commitment.</t>
+        </is>
+      </c>
+      <c r="C9" s="63" t="n"/>
+      <c r="D9" s="63" t="n"/>
+      <c r="E9" s="63" t="n"/>
+      <c r="F9" s="63" t="n"/>
+      <c r="G9" s="63" t="n"/>
+      <c r="H9" s="63" t="n"/>
+      <c r="I9" s="63" t="n"/>
+      <c r="J9" s="63" t="n"/>
+      <c r="K9" s="63" t="n"/>
+      <c r="L9" s="63" t="n"/>
+      <c r="M9" s="63" t="n"/>
+      <c r="N9" s="63" t="n"/>
+      <c r="O9" s="63" t="n"/>
+      <c r="P9" s="64" t="n"/>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>ROI Score</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Easy Win?</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Task / Gap to Fill</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Effort Level</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Effort (hours)</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>Compute</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>GPU Hours</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>Data Source (where to scrape)</t>
+        </is>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>Labeling Required?</t>
+        </is>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t># Annotators / Expertise</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>Annotation Time</t>
+        </is>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>Total Calendar Time</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>Target Venue (Q1 / CCF-A)</t>
+        </is>
+      </c>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t>Why Publishable</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Topic Modeling (Neural, large-scale)</t>
+        </is>
+      </c>
+      <c r="E12" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F12" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G12" s="70" t="inlineStr">
+        <is>
+          <t>40-60 hrs</t>
+        </is>
+      </c>
+      <c r="H12" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I12" s="70" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="J12" s="71" t="inlineStr">
+        <is>
+          <t>Scrape 100k+ BBC Urdu + Dawn news articles using newspaper3k Python lib; no labels needed — unsupervised</t>
+        </is>
+      </c>
+      <c r="K12" s="50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" s="49" t="inlineStr">
+        <is>
+          <t>0 — N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" s="72" t="inlineStr">
+        <is>
+          <t>4-5 weeks</t>
+        </is>
+      </c>
+      <c r="O12" s="73" t="inlineStr">
+        <is>
+          <t>IEEE Access / PLOS ONE (Q1 SCI)</t>
+        </is>
+      </c>
+      <c r="P12" s="74" t="inlineStr">
+        <is>
+          <t>No neural Urdu topic modeling at scale; unsupervised = no annotation cost = easy win</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Translate DROP to Urdu (Numerical Reasoning)</t>
+        </is>
+      </c>
+      <c r="E13" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F13" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G13" s="75" t="inlineStr">
+        <is>
+          <t>50-70 hrs</t>
+        </is>
+      </c>
+      <c r="H13" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I13" s="75" t="inlineStr">
+        <is>
+          <t>20-40 (fine-tune mT5)</t>
+        </is>
+      </c>
+      <c r="J13" s="76" t="inlineStr">
+        <is>
+          <t>DROP (https://allennlp.org/drop) — translate via LLM, post-edit numerical answers (numbers stay same)</t>
+        </is>
+      </c>
+      <c r="K13" s="53" t="inlineStr">
+        <is>
+          <t>Yes (minimal — answer validation)</t>
+        </is>
+      </c>
+      <c r="L13" s="51" t="inlineStr">
+        <is>
+          <t>2 students — Students</t>
+        </is>
+      </c>
+      <c r="M13" s="75" t="inlineStr">
+        <is>
+          <t>2 weeks</t>
+        </is>
+      </c>
+      <c r="N13" s="77" t="inlineStr">
+        <is>
+          <t>5-6 weeks</t>
+        </is>
+      </c>
+      <c r="O13" s="78" t="inlineStr">
+        <is>
+          <t>ACL Findings / EMNLP Findings (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P13" s="79" t="inlineStr">
+        <is>
+          <t>First Urdu numerical reasoning benchmark — fills obvious gap; DROP is well-known</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Document Clustering (large-scale)</t>
+        </is>
+      </c>
+      <c r="E14" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F14" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G14" s="70" t="inlineStr">
+        <is>
+          <t>50-70 hrs</t>
+        </is>
+      </c>
+      <c r="H14" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I14" s="70" t="inlineStr">
+        <is>
+          <t>15-30</t>
+        </is>
+      </c>
+      <c r="J14" s="71" t="inlineStr">
+        <is>
+          <t>Scrape 50k+ BBC Urdu + Dawn news articles (already categorized by news section = free labels); use 20NewsGroups-style evaluation</t>
+        </is>
+      </c>
+      <c r="K14" s="50" t="inlineStr">
+        <is>
+          <t>No (use news categories)</t>
+        </is>
+      </c>
+      <c r="L14" s="49" t="inlineStr">
+        <is>
+          <t>0 — N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="72" t="inlineStr">
+        <is>
+          <t>3-4 weeks</t>
+        </is>
+      </c>
+      <c r="O14" s="73" t="inlineStr">
+        <is>
+          <t>IEEE Access (Q1)</t>
+        </is>
+      </c>
+      <c r="P14" s="74" t="inlineStr">
+        <is>
+          <t>News categories = free labels; easy paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win (no annotation!)</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Document-to-Document Similarity (large-scale)</t>
+        </is>
+      </c>
+      <c r="E15" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F15" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G15" s="75" t="inlineStr">
+        <is>
+          <t>50-70 hrs</t>
+        </is>
+      </c>
+      <c r="H15" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I15" s="75" t="inlineStr">
+        <is>
+          <t>15-30</t>
+        </is>
+      </c>
+      <c r="J15" s="76" t="inlineStr">
+        <is>
+          <t>Urdu Wikipedia article pairs via interlanguage links (same article in Urdu + English); OR BBC Urdu same-day articles on same topic</t>
+        </is>
+      </c>
+      <c r="K15" s="53" t="inlineStr">
+        <is>
+          <t>No (similarity auto-computed)</t>
+        </is>
+      </c>
+      <c r="L15" s="51" t="inlineStr">
+        <is>
+          <t>0 — N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N15" s="77" t="inlineStr">
+        <is>
+          <t>3-4 weeks</t>
+        </is>
+      </c>
+      <c r="O15" s="78" t="inlineStr">
+        <is>
+          <t>IEEE Access (Q1)</t>
+        </is>
+      </c>
+      <c r="P15" s="79" t="inlineStr">
+        <is>
+          <t>Free labels via Wikipedia; easy paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C16" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Translate COMET-ATOMIC to Urdu (Commonsense Reasoning)</t>
+        </is>
+      </c>
+      <c r="E16" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F16" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G16" s="70" t="inlineStr">
+        <is>
+          <t>60-80 hrs</t>
+        </is>
+      </c>
+      <c r="H16" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I16" s="70" t="inlineStr">
+        <is>
+          <t>20-50 (A100 hrs for fine-tuning)</t>
+        </is>
+      </c>
+      <c r="J16" s="71" t="inlineStr">
+        <is>
+          <t>COMET-ATOMIC 2024 (https://github.com/allenai/comet_atomic2020) — translate via GPT-4o then human-post-edit 5%</t>
+        </is>
+      </c>
+      <c r="K16" s="54" t="inlineStr">
+        <is>
+          <t>Yes (post-editing only)</t>
+        </is>
+      </c>
+      <c r="L16" s="49" t="inlineStr">
+        <is>
+          <t>2-3 native Urdu speakers (students OK) — Student annotators</t>
+        </is>
+      </c>
+      <c r="M16" s="70" t="inlineStr">
+        <is>
+          <t>2-3 weeks</t>
+        </is>
+      </c>
+      <c r="N16" s="72" t="inlineStr">
+        <is>
+          <t>6-8 weeks</t>
+        </is>
+      </c>
+      <c r="O16" s="73" t="inlineStr">
+        <is>
+          <t>ACL Findings / EMNLP Findings (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P16" s="74" t="inlineStr">
+        <is>
+          <t>First Urdu commonsense KB — guaranteed novelty; COMET-ATOMIC is widely cited; cross-lingual commonsense is hot topic</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Build Urdu Semantic Textual Similarity (STS) Benchmark</t>
+        </is>
+      </c>
+      <c r="E17" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F17" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G17" s="75" t="inlineStr">
+        <is>
+          <t>60-80 hrs</t>
+        </is>
+      </c>
+      <c r="H17" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I17" s="75" t="inlineStr">
+        <is>
+          <t>20-40</t>
+        </is>
+      </c>
+      <c r="J17" s="76" t="inlineStr">
+        <is>
+          <t>Translate STSBenchmark (https://github.com/PhilipMay/stsb-multi-mt) via LLM + post-edit; supplement with Urdu news paraphrase pairs from BBC Urdu + Dawn</t>
+        </is>
+      </c>
+      <c r="K17" s="52" t="inlineStr">
+        <is>
+          <t>Yes (similarity score 0-5)</t>
+        </is>
+      </c>
+      <c r="L17" s="51" t="inlineStr">
+        <is>
+          <t>3 students — Students</t>
+        </is>
+      </c>
+      <c r="M17" s="75" t="inlineStr">
+        <is>
+          <t>2-3 weeks</t>
+        </is>
+      </c>
+      <c r="N17" s="77" t="inlineStr">
+        <is>
+          <t>5-6 weeks</t>
+        </is>
+      </c>
+      <c r="O17" s="78" t="inlineStr">
+        <is>
+          <t>LREC-COLING / SemEval (CCF-B)</t>
+        </is>
+      </c>
+      <c r="P17" s="79" t="inlineStr">
+        <is>
+          <t>No Urdu STS benchmark exists; STSBenchmark translations work for any language</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C18" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Math Word Problems</t>
+        </is>
+      </c>
+      <c r="E18" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F18" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G18" s="70" t="inlineStr">
+        <is>
+          <t>60-80 hrs</t>
+        </is>
+      </c>
+      <c r="H18" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I18" s="70" t="inlineStr">
+        <is>
+          <t>20-40</t>
+        </is>
+      </c>
+      <c r="J18" s="71" t="inlineStr">
+        <is>
+          <t>Translate ASDiv (https://github.com/google-research-datasets/asdiv) + AQuA via LLM; numbers stay same; minimal post-edit</t>
+        </is>
+      </c>
+      <c r="K18" s="54" t="inlineStr">
+        <is>
+          <t>Yes (answer verification)</t>
+        </is>
+      </c>
+      <c r="L18" s="49" t="inlineStr">
+        <is>
+          <t>1-2 students — Students (math background)</t>
+        </is>
+      </c>
+      <c r="M18" s="70" t="inlineStr">
+        <is>
+          <t>2 weeks</t>
+        </is>
+      </c>
+      <c r="N18" s="72" t="inlineStr">
+        <is>
+          <t>5-6 weeks</t>
+        </is>
+      </c>
+      <c r="O18" s="73" t="inlineStr">
+        <is>
+          <t>ACL Findings / EMNLP Findings</t>
+        </is>
+      </c>
+      <c r="P18" s="74" t="inlineStr">
+        <is>
+          <t>First Urdu MWP — easy translation, big educational impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Build UrduSpider (Text-to-SQL)</t>
+        </is>
+      </c>
+      <c r="E19" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F19" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G19" s="75" t="inlineStr">
+        <is>
+          <t>80-100 hrs</t>
+        </is>
+      </c>
+      <c r="H19" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I19" s="75" t="inlineStr">
+        <is>
+          <t>30-50 (T5/mT5 fine-tune)</t>
+        </is>
+      </c>
+      <c r="J19" s="76" t="inlineStr">
+        <is>
+          <t>Spider benchmark (https://yale-lily.github.io/spider) — translate questions + schema via LLM, post-edit critical 10%</t>
+        </is>
+      </c>
+      <c r="K19" s="52" t="inlineStr">
+        <is>
+          <t>Yes (SQL validation)</t>
+        </is>
+      </c>
+      <c r="L19" s="51" t="inlineStr">
+        <is>
+          <t>1-2 CS students with SQL skills — CS students</t>
+        </is>
+      </c>
+      <c r="M19" s="75" t="inlineStr">
+        <is>
+          <t>3-4 weeks</t>
+        </is>
+      </c>
+      <c r="N19" s="77" t="inlineStr">
+        <is>
+          <t>8-10 weeks</t>
+        </is>
+      </c>
+      <c r="O19" s="78" t="inlineStr">
+        <is>
+          <t>NAACL / ACL Findings (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P19" s="79" t="inlineStr">
+        <is>
+          <t>First Urdu text-to-SQL — high practical value for local software industry; Spider is benchmark-of-choice</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B20" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win (no annotation!)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Topic Segmentation (large)</t>
+        </is>
+      </c>
+      <c r="E20" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F20" s="80" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="G20" s="70" t="inlineStr">
+        <is>
+          <t>80-100 hrs</t>
+        </is>
+      </c>
+      <c r="H20" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I20" s="70" t="inlineStr">
+        <is>
+          <t>20-40</t>
+        </is>
+      </c>
+      <c r="J20" s="71" t="inlineStr">
+        <is>
+          <t>Scrape Wikipedia Urdu articles with section headers — section boundaries ARE topic segmentation labels (free labels!)</t>
+        </is>
+      </c>
+      <c r="K20" s="50" t="inlineStr">
+        <is>
+          <t>No (use section headers)</t>
+        </is>
+      </c>
+      <c r="L20" s="49" t="inlineStr">
+        <is>
+          <t>0 — N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="72" t="inlineStr">
+        <is>
+          <t>4-5 weeks</t>
+        </is>
+      </c>
+      <c r="O20" s="73" t="inlineStr">
+        <is>
+          <t>IEEE Access / PLOS ONE</t>
+        </is>
+      </c>
+      <c r="P20" s="74" t="inlineStr">
+        <is>
+          <t>Wikipedia section headers = free labels; current UrduSeg only 2k docs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="C21" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 5 easy win (no annotation!)</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Geolocation Prediction from Text</t>
+        </is>
+      </c>
+      <c r="E21" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F21" s="81" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="G21" s="75" t="inlineStr">
+        <is>
+          <t>80-100 hrs</t>
+        </is>
+      </c>
+      <c r="H21" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I21" s="75" t="inlineStr">
+        <is>
+          <t>20-40</t>
+        </is>
+      </c>
+      <c r="J21" s="76" t="inlineStr">
+        <is>
+          <t>Scrape Twitter Urdu tweets with geolocation enabled (use Twitter Academic API or snscrape); OR use Urdu news with city tags (Jang city-specific pages)</t>
+        </is>
+      </c>
+      <c r="K21" s="53" t="inlineStr">
+        <is>
+          <t>Yes (geo coordinate — auto from metadata)</t>
+        </is>
+      </c>
+      <c r="L21" s="51" t="inlineStr">
+        <is>
+          <t>0 (metadata = label) — N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N21" s="77" t="inlineStr">
+        <is>
+          <t>4-5 weeks</t>
+        </is>
+      </c>
+      <c r="O21" s="78" t="inlineStr">
+        <is>
+          <t>IEEE Access / TIST</t>
+        </is>
+      </c>
+      <c r="P21" s="79" t="inlineStr">
+        <is>
+          <t>Geo metadata = free labels; first Urdu geolocation work</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B22" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>Build Urdu-SemEval ABSA (Aspect-based Sentiment, large)</t>
+        </is>
+      </c>
+      <c r="E22" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F22" s="80" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="G22" s="70" t="inlineStr">
+        <is>
+          <t>100-150 hrs</t>
+        </is>
+      </c>
+      <c r="H22" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I22" s="70" t="inlineStr">
+        <is>
+          <t>30-60 (BERT fine-tune)</t>
+        </is>
+      </c>
+      <c r="J22" s="71" t="inlineStr">
+        <is>
+          <t>Scrape Daraz.pk reviews + Yelp-style Urdu reviews from Google Play Store Urdu apps; SemEval-2014 ABSA schema</t>
+        </is>
+      </c>
+      <c r="K22" s="54" t="inlineStr">
+        <is>
+          <t>Yes (aspect + polarity)</t>
+        </is>
+      </c>
+      <c r="L22" s="49" t="inlineStr">
+        <is>
+          <t>3-4 students — Students with light training</t>
+        </is>
+      </c>
+      <c r="M22" s="70" t="inlineStr">
+        <is>
+          <t>4-5 weeks</t>
+        </is>
+      </c>
+      <c r="N22" s="72" t="inlineStr">
+        <is>
+          <t>8-10 weeks</t>
+        </is>
+      </c>
+      <c r="O22" s="73" t="inlineStr">
+        <is>
+          <t>NAACL / LREC-COLING (CCF-B) → Knowledge-Based Systems (Q1 SCI)</t>
+        </is>
+      </c>
+      <c r="P22" s="74" t="inlineStr">
+        <is>
+          <t>Current Urdu ABSA is only 2k reviews — too small; SemEval-style benchmark easily publishable</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C23" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win (no annotation!)</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Authorship Attribution (cross-genre)</t>
+        </is>
+      </c>
+      <c r="E23" s="75" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F23" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G23" s="75" t="inlineStr">
+        <is>
+          <t>100-150 hrs</t>
+        </is>
+      </c>
+      <c r="H23" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I23" s="75" t="inlineStr">
+        <is>
+          <t>30-60</t>
+        </is>
+      </c>
+      <c r="J23" s="76" t="inlineStr">
+        <is>
+          <t>Project Gutenberg Urdu (https://www.gutenberg.org/browse/languages/ur); Urdu literary archives (Rekhta.org — 80k+ texts); author lists on Jang/Dawn columnists</t>
+        </is>
+      </c>
+      <c r="K23" s="82" t="inlineStr">
+        <is>
+          <t>Yes (author ID — already in metadata)</t>
+        </is>
+      </c>
+      <c r="L23" s="51" t="inlineStr">
+        <is>
+          <t>0 (label is metadata) — N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="77" t="inlineStr">
+        <is>
+          <t>4-6 weeks</t>
+        </is>
+      </c>
+      <c r="O23" s="78" t="inlineStr">
+        <is>
+          <t>PLOS ONE / IEEE Access (Q1)</t>
+        </is>
+      </c>
+      <c r="P23" s="79" t="inlineStr">
+        <is>
+          <t>Metadata labels = no annotation; cross-genre is novel angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win (no annotation!)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Cross-lingual Document Alignment at Scale</t>
+        </is>
+      </c>
+      <c r="E24" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F24" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G24" s="70" t="inlineStr">
+        <is>
+          <t>150-200 hrs</t>
+        </is>
+      </c>
+      <c r="H24" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I24" s="70" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="J24" s="71" t="inlineStr">
+        <is>
+          <t>Wikipedia inter-language links (Urdu↔English); BBC Urdu (https://www.bbc.com/urdu) + BBC English parallel articles; OPUS (https://opus.nlpl.eu) Urdu-English</t>
+        </is>
+      </c>
+      <c r="K24" s="50" t="inlineStr">
+        <is>
+          <t>No (auto-aligned via Wikipedia interlinks + URL matching)</t>
+        </is>
+      </c>
+      <c r="L24" s="49" t="inlineStr">
+        <is>
+          <t>0 — N/A</t>
+        </is>
+      </c>
+      <c r="M24" s="70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" s="72" t="inlineStr">
+        <is>
+          <t>6-8 weeks</t>
+        </is>
+      </c>
+      <c r="O24" s="73" t="inlineStr">
+        <is>
+          <t>LREC-COLING / TACL (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P24" s="74" t="inlineStr">
+        <is>
+          <t>Wikipedia interlinks = free alignment; huge IR/MT value</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B25" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>Urdu News Headline Sarcasm (large)</t>
+        </is>
+      </c>
+      <c r="E25" s="75" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F25" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G25" s="75" t="inlineStr">
+        <is>
+          <t>50-70 hrs</t>
+        </is>
+      </c>
+      <c r="H25" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I25" s="75" t="inlineStr">
+        <is>
+          <t>15-30</t>
+        </is>
+      </c>
+      <c r="J25" s="76" t="inlineStr">
+        <is>
+          <t>Scrape Jang, Dawn, Express, Nawa-i-Waqt headlines; crowdsource sarcasm labels via Amazon Mechanical Turk or local students</t>
+        </is>
+      </c>
+      <c r="K25" s="82" t="inlineStr">
+        <is>
+          <t>Yes (binary)</t>
+        </is>
+      </c>
+      <c r="L25" s="51" t="inlineStr">
+        <is>
+          <t>3-5 students — Students (Urdu native)</t>
+        </is>
+      </c>
+      <c r="M25" s="75" t="inlineStr">
+        <is>
+          <t>2-3 weeks</t>
+        </is>
+      </c>
+      <c r="N25" s="77" t="inlineStr">
+        <is>
+          <t>5-6 weeks</t>
+        </is>
+      </c>
+      <c r="O25" s="78" t="inlineStr">
+        <is>
+          <t>IEEE Access (Q1 SCI) / Information Processing &amp; Management (Q1)</t>
+        </is>
+      </c>
+      <c r="P25" s="79" t="inlineStr">
+        <is>
+          <t>Current Urdu sarcasm only 3k tweets — easy to scale to 20k+ headlines</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Code-mixed Detection (Roman-Nastaliq switching)</t>
+        </is>
+      </c>
+      <c r="E26" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F26" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G26" s="70" t="inlineStr">
+        <is>
+          <t>50-70 hrs</t>
+        </is>
+      </c>
+      <c r="H26" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I26" s="70" t="inlineStr">
+        <is>
+          <t>10-20</t>
+        </is>
+      </c>
+      <c r="J26" s="71" t="inlineStr">
+        <is>
+          <t>Scrape Twitter/X via snscrape for 'Roman Urdu' queries; scrape YouTube Urdu comments via yt-dlp; CMU code-mixed schema</t>
+        </is>
+      </c>
+      <c r="K26" s="55" t="inlineStr">
+        <is>
+          <t>Yes (binary: code-mixed or not)</t>
+        </is>
+      </c>
+      <c r="L26" s="49" t="inlineStr">
+        <is>
+          <t>2 students — Students</t>
+        </is>
+      </c>
+      <c r="M26" s="70" t="inlineStr">
+        <is>
+          <t>2 weeks</t>
+        </is>
+      </c>
+      <c r="N26" s="72" t="inlineStr">
+        <is>
+          <t>5-6 weeks</t>
+        </is>
+      </c>
+      <c r="O26" s="73" t="inlineStr">
+        <is>
+          <t>LREC-COLING / FIRE (Indian venue)</t>
+        </is>
+      </c>
+      <c r="P26" s="74" t="inlineStr">
+        <is>
+          <t>Existing work focuses on Roman-Eng; Nastaliq-Roman switching unexplored</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Multi-domain Sentiment (50k+)</t>
+        </is>
+      </c>
+      <c r="E27" s="75" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F27" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G27" s="75" t="inlineStr">
+        <is>
+          <t>60-80 hrs</t>
+        </is>
+      </c>
+      <c r="H27" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I27" s="75" t="inlineStr">
+        <is>
+          <t>20-30</t>
+        </is>
+      </c>
+      <c r="J27" s="76" t="inlineStr">
+        <is>
+          <t>Scrape Daraz.pk (products), Foodpanda.pk (restaurants), Bookmeter.pk, Google Play Urdu app reviews, YouTube Urdu comments via yt-dlp</t>
+        </is>
+      </c>
+      <c r="K27" s="82" t="inlineStr">
+        <is>
+          <t>Yes (3-class sentiment)</t>
+        </is>
+      </c>
+      <c r="L27" s="51" t="inlineStr">
+        <is>
+          <t>3 students — Students</t>
+        </is>
+      </c>
+      <c r="M27" s="75" t="inlineStr">
+        <is>
+          <t>3 weeks</t>
+        </is>
+      </c>
+      <c r="N27" s="77" t="inlineStr">
+        <is>
+          <t>6-8 weeks</t>
+        </is>
+      </c>
+      <c r="O27" s="78" t="inlineStr">
+        <is>
+          <t>IEEE Access (Q1 SCI, easy acceptance) / PLOS ONE</t>
+        </is>
+      </c>
+      <c r="P27" s="79" t="inlineStr">
+        <is>
+          <t>UrduSent is 10k tweets only — multi-domain is publishable in IEEE Access easily</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B28" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Keyphrase Extraction (Neural, large-scale)</t>
+        </is>
+      </c>
+      <c r="E28" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F28" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G28" s="70" t="inlineStr">
+        <is>
+          <t>60-80 hrs</t>
+        </is>
+      </c>
+      <c r="H28" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I28" s="70" t="inlineStr">
+        <is>
+          <t>15-30</t>
+        </is>
+      </c>
+      <c r="J28" s="71" t="inlineStr">
+        <is>
+          <t>Scrape BBC Urdu (https://www.bbc.com/urdu) + Dawn Urdu news + Jang.com.pk articles; KP-20k-style annotation</t>
+        </is>
+      </c>
+      <c r="K28" s="54" t="inlineStr">
+        <is>
+          <t>Yes (keyphrase)</t>
+        </is>
+      </c>
+      <c r="L28" s="49" t="inlineStr">
+        <is>
+          <t>2 students — Students</t>
+        </is>
+      </c>
+      <c r="M28" s="70" t="inlineStr">
+        <is>
+          <t>3 weeks</t>
+        </is>
+      </c>
+      <c r="N28" s="72" t="inlineStr">
+        <is>
+          <t>6-7 weeks</t>
+        </is>
+      </c>
+      <c r="O28" s="73" t="inlineStr">
+        <is>
+          <t>IEEE Access / PLOS ONE (Q1 SCI)</t>
+        </is>
+      </c>
+      <c r="P28" s="74" t="inlineStr">
+        <is>
+          <t>Existing Urdu KP work uses tiny corpus; KP-20k format well-established</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B29" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Readability Assessment (large)</t>
+        </is>
+      </c>
+      <c r="E29" s="75" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F29" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G29" s="75" t="inlineStr">
+        <is>
+          <t>60-80 hrs</t>
+        </is>
+      </c>
+      <c r="H29" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I29" s="75" t="inlineStr">
+        <is>
+          <t>15-25</t>
+        </is>
+      </c>
+      <c r="J29" s="76" t="inlineStr">
+        <is>
+          <t>Scrape Urdu Wikipedia + BBC Urdu (different grade levels via article categories); label by Flesch-style score adapted for Urdu</t>
+        </is>
+      </c>
+      <c r="K29" s="52" t="inlineStr">
+        <is>
+          <t>Yes (readability score)</t>
+        </is>
+      </c>
+      <c r="L29" s="51" t="inlineStr">
+        <is>
+          <t>2 students — Students + 1 education expert</t>
+        </is>
+      </c>
+      <c r="M29" s="75" t="inlineStr">
+        <is>
+          <t>3 weeks</t>
+        </is>
+      </c>
+      <c r="N29" s="77" t="inlineStr">
+        <is>
+          <t>6-7 weeks</t>
+        </is>
+      </c>
+      <c r="O29" s="78" t="inlineStr">
+        <is>
+          <t>IEEE Access / PLOS ONE</t>
+        </is>
+      </c>
+      <c r="P29" s="79" t="inlineStr">
+        <is>
+          <t>Existing UrduRead only 3k sentences; needs scaling</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="B30" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C30" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Personality Detection from Text</t>
+        </is>
+      </c>
+      <c r="E30" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F30" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G30" s="70" t="inlineStr">
+        <is>
+          <t>60-80 hrs</t>
+        </is>
+      </c>
+      <c r="H30" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I30" s="70" t="inlineStr">
+        <is>
+          <t>20-30</t>
+        </is>
+      </c>
+      <c r="J30" s="71" t="inlineStr">
+        <is>
+          <t>Translate Essays dataset (https://github.com/SvenBuechel/essays) via LLM; OR scrape Urdu blogs + author MBTI tags from personality forums</t>
+        </is>
+      </c>
+      <c r="K30" s="54" t="inlineStr">
+        <is>
+          <t>Yes (MBTI / Big Five)</t>
+        </is>
+      </c>
+      <c r="L30" s="49" t="inlineStr">
+        <is>
+          <t>2 students — Psychology students preferred</t>
+        </is>
+      </c>
+      <c r="M30" s="70" t="inlineStr">
+        <is>
+          <t>2-3 weeks</t>
+        </is>
+      </c>
+      <c r="N30" s="72" t="inlineStr">
+        <is>
+          <t>5-6 weeks</t>
+        </is>
+      </c>
+      <c r="O30" s="73" t="inlineStr">
+        <is>
+          <t>IEEE Access / PLOS ONE</t>
+        </is>
+      </c>
+      <c r="P30" s="74" t="inlineStr">
+        <is>
+          <t>First Urdu personality detection — easy novelty</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B31" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" s="53" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>Translate XSum to Urdu (Abstractive Summarization)</t>
+        </is>
+      </c>
+      <c r="E31" s="75" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F31" s="81" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="G31" s="75" t="inlineStr">
+        <is>
+          <t>80-100 hrs</t>
+        </is>
+      </c>
+      <c r="H31" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I31" s="75" t="inlineStr">
+        <is>
+          <t>100-200 (mBART fine-tune)</t>
+        </is>
+      </c>
+      <c r="J31" s="76" t="inlineStr">
+        <is>
+          <t>BBC XSum (https://github.com/EdinburghNLP/XSum) — translate via LLM; OR scrape BBC Urdu existing summaries directly (BBC Urdu articles have summaries)</t>
+        </is>
+      </c>
+      <c r="K31" s="53" t="inlineStr">
+        <is>
+          <t>Yes (minimal post-edit)</t>
+        </is>
+      </c>
+      <c r="L31" s="51" t="inlineStr">
+        <is>
+          <t>2 students — Students</t>
+        </is>
+      </c>
+      <c r="M31" s="75" t="inlineStr">
+        <is>
+          <t>3-4 weeks</t>
+        </is>
+      </c>
+      <c r="N31" s="77" t="inlineStr">
+        <is>
+          <t>8-10 weeks</t>
+        </is>
+      </c>
+      <c r="O31" s="78" t="inlineStr">
+        <is>
+          <t>ACL Findings / EMNLP Findings (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P31" s="79" t="inlineStr">
+        <is>
+          <t>UrduSumm only 5k articles; XSum-style benchmark would be first standardized Urdu summarization</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B32" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" s="50" t="inlineStr">
+        <is>
+          <t>Yes — top 10 easy win</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Plagiarism Detection (large-scale)</t>
+        </is>
+      </c>
+      <c r="E32" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F32" s="80" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="G32" s="70" t="inlineStr">
+        <is>
+          <t>80-100 hrs</t>
+        </is>
+      </c>
+      <c r="H32" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I32" s="70" t="inlineStr">
+        <is>
+          <t>20-40</t>
+        </is>
+      </c>
+      <c r="J32" s="71" t="inlineStr">
+        <is>
+          <t>Use Urdu Wikipedia edit history (https://dumps.wikimedia.org/urwiki/) — revert wars = plagiarism; supplement with Urdu research papers from HEC Pakistan repository (https://www.hec.gov.pk)</t>
+        </is>
+      </c>
+      <c r="K32" s="54" t="inlineStr">
+        <is>
+          <t>Yes (plagiarism type)</t>
+        </is>
+      </c>
+      <c r="L32" s="49" t="inlineStr">
+        <is>
+          <t>1-2 students — Students</t>
+        </is>
+      </c>
+      <c r="M32" s="70" t="inlineStr">
+        <is>
+          <t>2-3 weeks</t>
+        </is>
+      </c>
+      <c r="N32" s="72" t="inlineStr">
+        <is>
+          <t>6-7 weeks</t>
+        </is>
+      </c>
+      <c r="O32" s="73" t="inlineStr">
+        <is>
+          <t>PLOS ONE / Scientometrics (Q1)</t>
+        </is>
+      </c>
+      <c r="P32" s="74" t="inlineStr">
+        <is>
+          <t>Wikipedia edit history = free plagiarism labels; novel for Urdu</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B33" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Stance Detection (multi-target)</t>
+        </is>
+      </c>
+      <c r="E33" s="75" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F33" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G33" s="75" t="inlineStr">
+        <is>
+          <t>100-150 hrs</t>
+        </is>
+      </c>
+      <c r="H33" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I33" s="75" t="inlineStr">
+        <is>
+          <t>30-60</t>
+        </is>
+      </c>
+      <c r="J33" s="76" t="inlineStr">
+        <is>
+          <t>Scrape Twitter debates on Pakistani politics (Imran Khan, PML-N, PPP); SemEval-2016 Task 6 schema; use RumourEval-2019 schema</t>
+        </is>
+      </c>
+      <c r="K33" s="52" t="inlineStr">
+        <is>
+          <t>Yes (stance: favor/against/none)</t>
+        </is>
+      </c>
+      <c r="L33" s="51" t="inlineStr">
+        <is>
+          <t>3 students — Students with political awareness</t>
+        </is>
+      </c>
+      <c r="M33" s="75" t="inlineStr">
+        <is>
+          <t>4-5 weeks</t>
+        </is>
+      </c>
+      <c r="N33" s="77" t="inlineStr">
+        <is>
+          <t>8-10 weeks</t>
+        </is>
+      </c>
+      <c r="O33" s="78" t="inlineStr">
+        <is>
+          <t>IEEE Access / Information Processing &amp; Management (Q1)</t>
+        </is>
+      </c>
+      <c r="P33" s="79" t="inlineStr">
+        <is>
+          <t>Current Urdu stance work is tiny (2k posts); multi-target is novel angle</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B34" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Emotion Cause Extraction (ECE)</t>
+        </is>
+      </c>
+      <c r="E34" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F34" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G34" s="70" t="inlineStr">
+        <is>
+          <t>100-150 hrs</t>
+        </is>
+      </c>
+      <c r="H34" s="50" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I34" s="70" t="inlineStr">
+        <is>
+          <t>30-50</t>
+        </is>
+      </c>
+      <c r="J34" s="71" t="inlineStr">
+        <is>
+          <t>Scrape Urdu Twitter emotional posts (use emotion lexicon to filter); RECCON schema annotation</t>
+        </is>
+      </c>
+      <c r="K34" s="54" t="inlineStr">
+        <is>
+          <t>Yes (emotion + cause span)</t>
+        </is>
+      </c>
+      <c r="L34" s="49" t="inlineStr">
+        <is>
+          <t>3 students — Students</t>
+        </is>
+      </c>
+      <c r="M34" s="70" t="inlineStr">
+        <is>
+          <t>4-5 weeks</t>
+        </is>
+      </c>
+      <c r="N34" s="72" t="inlineStr">
+        <is>
+          <t>8-10 weeks</t>
+        </is>
+      </c>
+      <c r="O34" s="73" t="inlineStr">
+        <is>
+          <t>IEEE Access (Q1) / PLOS ONE</t>
+        </is>
+      </c>
+      <c r="P34" s="74" t="inlineStr">
+        <is>
+          <t>Urdu ECE is at 2k pairs — very small, easy to scale to 10k+</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B35" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="83" t="inlineStr">
+        <is>
+          <t>No — needs LLM compute</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Long-form QA</t>
+        </is>
+      </c>
+      <c r="E35" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F35" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G35" s="75" t="inlineStr">
+        <is>
+          <t>150-200 hrs</t>
+        </is>
+      </c>
+      <c r="H35" s="52" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I35" s="75" t="inlineStr">
+        <is>
+          <t>300-600 (LLM fine-tune)</t>
+        </is>
+      </c>
+      <c r="J35" s="76" t="inlineStr">
+        <is>
+          <t>Urdu Wikipedia (https://ur.wikipedia.org) — 200k+ articles; build ELI5-style long-form QA via GPT-4o generation + human verification</t>
+        </is>
+      </c>
+      <c r="K35" s="52" t="inlineStr">
+        <is>
+          <t>Yes (answer verification)</t>
+        </is>
+      </c>
+      <c r="L35" s="51" t="inlineStr">
+        <is>
+          <t>2-3 students — Students</t>
+        </is>
+      </c>
+      <c r="M35" s="75" t="inlineStr">
+        <is>
+          <t>6-8 weeks</t>
+        </is>
+      </c>
+      <c r="N35" s="77" t="inlineStr">
+        <is>
+          <t>12-14 weeks</t>
+        </is>
+      </c>
+      <c r="O35" s="78" t="inlineStr">
+        <is>
+          <t>ACL / EMNLP Findings</t>
+        </is>
+      </c>
+      <c r="P35" s="79" t="inlineStr">
+        <is>
+          <t>Only extractive QA exists; long-form is hot in LLM era</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B36" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Multi-hop Reading Comprehension</t>
+        </is>
+      </c>
+      <c r="E36" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F36" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G36" s="70" t="inlineStr">
+        <is>
+          <t>150-200 hrs</t>
+        </is>
+      </c>
+      <c r="H36" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I36" s="70" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="J36" s="71" t="inlineStr">
+        <is>
+          <t>Translate HotpotQA (https://hotpotqa.github.io) via LLM; OR build from Urdu Wikipedia multi-page link graph</t>
+        </is>
+      </c>
+      <c r="K36" s="54" t="inlineStr">
+        <is>
+          <t>Yes (answer + supporting docs)</t>
+        </is>
+      </c>
+      <c r="L36" s="49" t="inlineStr">
+        <is>
+          <t>2-3 students — Students</t>
+        </is>
+      </c>
+      <c r="M36" s="70" t="inlineStr">
+        <is>
+          <t>5-6 weeks</t>
+        </is>
+      </c>
+      <c r="N36" s="72" t="inlineStr">
+        <is>
+          <t>10-12 weeks</t>
+        </is>
+      </c>
+      <c r="O36" s="73" t="inlineStr">
+        <is>
+          <t>ACL Findings / EMNLP Findings</t>
+        </is>
+      </c>
+      <c r="P36" s="74" t="inlineStr">
+        <is>
+          <t>UQuAD only single-hop; multi-hop is natural extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="B37" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Multi-modal Sentiment (text + image)</t>
+        </is>
+      </c>
+      <c r="E37" s="75" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F37" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G37" s="75" t="inlineStr">
+        <is>
+          <t>150-200 hrs</t>
+        </is>
+      </c>
+      <c r="H37" s="52" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I37" s="75" t="inlineStr">
+        <is>
+          <t>200-400 (multimodal BERT)</t>
+        </is>
+      </c>
+      <c r="J37" s="76" t="inlineStr">
+        <is>
+          <t>Scrape Urdu tweets with images via Twitter API; Urdu Instagram posts (legal grey area); YouTube Urdu video thumbnails + comments</t>
+        </is>
+      </c>
+      <c r="K37" s="82" t="inlineStr">
+        <is>
+          <t>Yes (3-class sentiment)</t>
+        </is>
+      </c>
+      <c r="L37" s="51" t="inlineStr">
+        <is>
+          <t>3 students — Students</t>
+        </is>
+      </c>
+      <c r="M37" s="75" t="inlineStr">
+        <is>
+          <t>5-6 weeks</t>
+        </is>
+      </c>
+      <c r="N37" s="77" t="inlineStr">
+        <is>
+          <t>10-12 weeks</t>
+        </is>
+      </c>
+      <c r="O37" s="78" t="inlineStr">
+        <is>
+          <t>IEEE Access (Q1) / ACM MM workshop</t>
+        </is>
+      </c>
+      <c r="P37" s="79" t="inlineStr">
+        <is>
+          <t>Only 5k pairs exist; multimodal is trendy</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B38" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Fake News Detection (multimodal)</t>
+        </is>
+      </c>
+      <c r="E38" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F38" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G38" s="70" t="inlineStr">
+        <is>
+          <t>150-200 hrs</t>
+        </is>
+      </c>
+      <c r="H38" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I38" s="70" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="J38" s="71" t="inlineStr">
+        <is>
+          <t>Scrape debunked stories from Soch Fact Check (https://sochfactcheck.com), AFP Pakistan Urdu fact-checks; pair with original fake posts on Facebook/Twitter Urdu</t>
+        </is>
+      </c>
+      <c r="K38" s="54" t="inlineStr">
+        <is>
+          <t>Yes (fake/real + claim type)</t>
+        </is>
+      </c>
+      <c r="L38" s="49" t="inlineStr">
+        <is>
+          <t>2-3 fact-checkers (light training) — Junior fact-checkers</t>
+        </is>
+      </c>
+      <c r="M38" s="70" t="inlineStr">
+        <is>
+          <t>5-6 weeks</t>
+        </is>
+      </c>
+      <c r="N38" s="72" t="inlineStr">
+        <is>
+          <t>10-12 weeks</t>
+        </is>
+      </c>
+      <c r="O38" s="73" t="inlineStr">
+        <is>
+          <t>ACL Findings / PLOS ONE (Q1)</t>
+        </is>
+      </c>
+      <c r="P38" s="74" t="inlineStr">
+        <is>
+          <t>UrduFakeNet only 10k text-only; multimodal + real fact-checker labels is novel</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B39" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Entity Linking (Wikipedia-based)</t>
+        </is>
+      </c>
+      <c r="E39" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F39" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G39" s="75" t="inlineStr">
+        <is>
+          <t>150-200 hrs</t>
+        </is>
+      </c>
+      <c r="H39" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I39" s="75" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="J39" s="76" t="inlineStr">
+        <is>
+          <t>Urdu Wikipedia (200k+ articles); use AIDA-CoNLL schema; auto-generate candidates via Wikipedia links, then human-verify</t>
+        </is>
+      </c>
+      <c r="K39" s="52" t="inlineStr">
+        <is>
+          <t>Yes (entity verification)</t>
+        </is>
+      </c>
+      <c r="L39" s="51" t="inlineStr">
+        <is>
+          <t>2-3 students — Students</t>
+        </is>
+      </c>
+      <c r="M39" s="75" t="inlineStr">
+        <is>
+          <t>6-8 weeks</t>
+        </is>
+      </c>
+      <c r="N39" s="77" t="inlineStr">
+        <is>
+          <t>10-12 weeks</t>
+        </is>
+      </c>
+      <c r="O39" s="78" t="inlineStr">
+        <is>
+          <t>ACL Findings / EMNLP Findings (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P39" s="79" t="inlineStr">
+        <is>
+          <t>First Urdu EL — high practical value for IR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="B40" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C40" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Trustworthiness Evaluation Benchmark for LLMs</t>
+        </is>
+      </c>
+      <c r="E40" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F40" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G40" s="70" t="inlineStr">
+        <is>
+          <t>200-300 hrs</t>
+        </is>
+      </c>
+      <c r="H40" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I40" s="70" t="inlineStr">
+        <is>
+          <t>200-400</t>
+        </is>
+      </c>
+      <c r="J40" s="71" t="inlineStr">
+        <is>
+          <t>Translate TrustLLM benchmark (https://trustllm.github.io) via LLM + cultural adaptation; OR build new with Pakistani cultural context</t>
+        </is>
+      </c>
+      <c r="K40" s="54" t="inlineStr">
+        <is>
+          <t>Yes (toxicity / fairness / robustness labels)</t>
+        </is>
+      </c>
+      <c r="L40" s="49" t="inlineStr">
+        <is>
+          <t>3-4 students — Students</t>
+        </is>
+      </c>
+      <c r="M40" s="70" t="inlineStr">
+        <is>
+          <t>6-8 weeks</t>
+        </is>
+      </c>
+      <c r="N40" s="72" t="inlineStr">
+        <is>
+          <t>12-14 weeks</t>
+        </is>
+      </c>
+      <c r="O40" s="73" t="inlineStr">
+        <is>
+          <t>ACL Findings / NeurIPS Datasets Track</t>
+        </is>
+      </c>
+      <c r="P40" s="74" t="inlineStr">
+        <is>
+          <t>Trustworthy AI is hot topic; first Urdu trust benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="B41" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D41" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Verbal Irony Detection (distinct from sarcasm)</t>
+        </is>
+      </c>
+      <c r="E41" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F41" s="81" t="inlineStr">
+        <is>
+          <t>Low-Medium</t>
+        </is>
+      </c>
+      <c r="G41" s="75" t="inlineStr">
+        <is>
+          <t>80-100 hrs</t>
+        </is>
+      </c>
+      <c r="H41" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I41" s="75" t="inlineStr">
+        <is>
+          <t>20-40</t>
+        </is>
+      </c>
+      <c r="J41" s="76" t="inlineStr">
+        <is>
+          <t>Scrape Urdu Twitter + Reddit /r/pakistan; use Magpie (https://github.com/irina-shengling/magpie) schema adapted for Urdu</t>
+        </is>
+      </c>
+      <c r="K41" s="82" t="inlineStr">
+        <is>
+          <t>Yes (irony type + binary)</t>
+        </is>
+      </c>
+      <c r="L41" s="51" t="inlineStr">
+        <is>
+          <t>3 students — Students (literature background preferred)</t>
+        </is>
+      </c>
+      <c r="M41" s="75" t="inlineStr">
+        <is>
+          <t>3-4 weeks</t>
+        </is>
+      </c>
+      <c r="N41" s="77" t="inlineStr">
+        <is>
+          <t>7-8 weeks</t>
+        </is>
+      </c>
+      <c r="O41" s="78" t="inlineStr">
+        <is>
+          <t>IEEE Access / PLOS ONE</t>
+        </is>
+      </c>
+      <c r="P41" s="79" t="inlineStr">
+        <is>
+          <t>Distinct from sarcasm = novel angle; Urdu has rich irony tradition</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="B42" s="85" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Few-shot / Zero-shot NER Benchmark</t>
+        </is>
+      </c>
+      <c r="E42" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F42" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G42" s="70" t="inlineStr">
+        <is>
+          <t>150-200 hrs</t>
+        </is>
+      </c>
+      <c r="H42" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I42" s="70" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="J42" s="71" t="inlineStr">
+        <is>
+          <t>Use existing CURRE + WikiANN Urdu + new annotation in 5+ domains (news, biomedical, legal, social media, literature)</t>
+        </is>
+      </c>
+      <c r="K42" s="54" t="inlineStr">
+        <is>
+          <t>Yes (NER in new domains)</t>
+        </is>
+      </c>
+      <c r="L42" s="49" t="inlineStr">
+        <is>
+          <t>3-4 students — Students</t>
+        </is>
+      </c>
+      <c r="M42" s="70" t="inlineStr">
+        <is>
+          <t>8-10 weeks</t>
+        </is>
+      </c>
+      <c r="N42" s="72" t="inlineStr">
+        <is>
+          <t>14-16 weeks</t>
+        </is>
+      </c>
+      <c r="O42" s="73" t="inlineStr">
+        <is>
+          <t>ACL Findings / EMNLP Findings (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P42" s="74" t="inlineStr">
+        <is>
+          <t>Few-shot NER benchmark for Urdu is timely; LLM community cares</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="B43" s="85" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D43" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Disfluency Detection (spoken Urdu)</t>
+        </is>
+      </c>
+      <c r="E43" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F43" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G43" s="75" t="inlineStr">
+        <is>
+          <t>150-200 hrs</t>
+        </is>
+      </c>
+      <c r="H43" s="53" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="I43" s="75" t="inlineStr">
+        <is>
+          <t>30-60</t>
+        </is>
+      </c>
+      <c r="J43" s="76" t="inlineStr">
+        <is>
+          <t>UrduSpeech (156 hrs) — transcribe with Whisper-large, then annotate disfluencies; OR run new interviews with Pakistani speakers</t>
+        </is>
+      </c>
+      <c r="K43" s="52" t="inlineStr">
+        <is>
+          <t>Yes (disfluency span)</t>
+        </is>
+      </c>
+      <c r="L43" s="51" t="inlineStr">
+        <is>
+          <t>3 students — Students with phonetics training</t>
+        </is>
+      </c>
+      <c r="M43" s="75" t="inlineStr">
+        <is>
+          <t>8-10 weeks</t>
+        </is>
+      </c>
+      <c r="N43" s="77" t="inlineStr">
+        <is>
+          <t>14-16 weeks</t>
+        </is>
+      </c>
+      <c r="O43" s="78" t="inlineStr">
+        <is>
+          <t>Interspeech / ACL Findings</t>
+        </is>
+      </c>
+      <c r="P43" s="79" t="inlineStr">
+        <is>
+          <t>First Urdu disfluency work — important for spoken Urdu understanding</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="B44" s="85" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" s="55" t="inlineStr">
+        <is>
+          <t>Medium effort but very high impact</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Grammatical Error Correction (GEC)</t>
+        </is>
+      </c>
+      <c r="E44" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F44" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G44" s="70" t="inlineStr">
+        <is>
+          <t>200-300 hrs</t>
+        </is>
+      </c>
+      <c r="H44" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I44" s="70" t="inlineStr">
+        <is>
+          <t>200-500 (seq2seq training)</t>
+        </is>
+      </c>
+      <c r="J44" s="71" t="inlineStr">
+        <is>
+          <t>Scrape Urdu learner essays from italki.com, Lang-8 (if accessible), Urdu Wikipedia edit history (reverted edits = errors); partner with Allama Iqbal Open University for learner data</t>
+        </is>
+      </c>
+      <c r="K44" s="54" t="inlineStr">
+        <is>
+          <t>Yes (GEC annotation is hard)</t>
+        </is>
+      </c>
+      <c r="L44" s="49" t="inlineStr">
+        <is>
+          <t>3-4 experts (Urdu language teachers) — Urdu language teachers</t>
+        </is>
+      </c>
+      <c r="M44" s="70" t="inlineStr">
+        <is>
+          <t>12-16 weeks</t>
+        </is>
+      </c>
+      <c r="N44" s="72" t="inlineStr">
+        <is>
+          <t>20-24 weeks</t>
+        </is>
+      </c>
+      <c r="O44" s="73" t="inlineStr">
+        <is>
+          <t>ACL / EMNLP main (CCF-A) / BEA workshop</t>
+        </is>
+      </c>
+      <c r="P44" s="74" t="inlineStr">
+        <is>
+          <t>First Urdu GEC — guaranteed ACL/EMNLP acceptance if quality is good</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="B45" s="85" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" s="83" t="inlineStr">
+        <is>
+          <t>No — needs proper annotation team</t>
+        </is>
+      </c>
+      <c r="D45" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Cross-Document Event Extraction</t>
+        </is>
+      </c>
+      <c r="E45" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F45" s="52" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="G45" s="75" t="inlineStr">
+        <is>
+          <t>300-400 hrs</t>
+        </is>
+      </c>
+      <c r="H45" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I45" s="75" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="J45" s="76" t="inlineStr">
+        <is>
+          <t>Scrape Jang/Dawn news articles on same events (cross-doc); use ACE-2005 schema; cross-link via Wikidata Urdu events</t>
+        </is>
+      </c>
+      <c r="K45" s="52" t="inlineStr">
+        <is>
+          <t>Yes (event + arguments)</t>
+        </is>
+      </c>
+      <c r="L45" s="51" t="inlineStr">
+        <is>
+          <t>3-4 trained annotators — Trained NLP annotators</t>
+        </is>
+      </c>
+      <c r="M45" s="75" t="inlineStr">
+        <is>
+          <t>10-12 weeks</t>
+        </is>
+      </c>
+      <c r="N45" s="77" t="inlineStr">
+        <is>
+          <t>16-20 weeks</t>
+        </is>
+      </c>
+      <c r="O45" s="78" t="inlineStr">
+        <is>
+          <t>ACL Findings / NAACL (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P45" s="79" t="inlineStr">
+        <is>
+          <t>First Urdu cross-doc EE — fills obvious gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="B46" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Speech Translation (end-to-end)</t>
+        </is>
+      </c>
+      <c r="E46" s="70" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F46" s="54" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="G46" s="70" t="inlineStr">
+        <is>
+          <t>250-350 hrs</t>
+        </is>
+      </c>
+      <c r="H46" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I46" s="70" t="inlineStr">
+        <is>
+          <t>500-1000</t>
+        </is>
+      </c>
+      <c r="J46" s="71" t="inlineStr">
+        <is>
+          <t>Extend CoVoST (https://github.com/facebookresearch/covost) with UrduSpeech audio + Urdu-English translations; OR use SeamlessM4T framework on UrduSpeech</t>
+        </is>
+      </c>
+      <c r="K46" s="54" t="inlineStr">
+        <is>
+          <t>Yes (audio + translation pairs)</t>
+        </is>
+      </c>
+      <c r="L46" s="49" t="inlineStr">
+        <is>
+          <t>2-3 translators — Bilingual translators</t>
+        </is>
+      </c>
+      <c r="M46" s="70" t="inlineStr">
+        <is>
+          <t>10-12 weeks</t>
+        </is>
+      </c>
+      <c r="N46" s="72" t="inlineStr">
+        <is>
+          <t>16-20 weeks</t>
+        </is>
+      </c>
+      <c r="O46" s="73" t="inlineStr">
+        <is>
+          <t>ACL Main / EMNLP Main / Interspeech</t>
+        </is>
+      </c>
+      <c r="P46" s="74" t="inlineStr">
+        <is>
+          <t>End-to-end Urdu ST is missing; SeamlessM4T framework is hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="n">
+        <v>36</v>
+      </c>
+      <c r="B47" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="83" t="inlineStr">
+        <is>
+          <t>No — requires fact-checking org partnership</t>
+        </is>
+      </c>
+      <c r="D47" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Fact-checking (claim-evidence)</t>
+        </is>
+      </c>
+      <c r="E47" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F47" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G47" s="75" t="inlineStr">
+        <is>
+          <t>300-400 hrs</t>
+        </is>
+      </c>
+      <c r="H47" s="82" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I47" s="75" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="J47" s="76" t="inlineStr">
+        <is>
+          <t>Scrape Soch Fact Check, AFP Pakistan, TruthOrFiction Urdu; pair with original false claims on Facebook Urdu, WhatsApp Urdu forwards (via fact-checking orgs)</t>
+        </is>
+      </c>
+      <c r="K47" s="52" t="inlineStr">
+        <is>
+          <t>Yes (claim + evidence + verdict)</t>
+        </is>
+      </c>
+      <c r="L47" s="51" t="inlineStr">
+        <is>
+          <t>3-4 trained fact-checkers — Trained fact-checkers</t>
+        </is>
+      </c>
+      <c r="M47" s="75" t="inlineStr">
+        <is>
+          <t>12-16 weeks</t>
+        </is>
+      </c>
+      <c r="N47" s="77" t="inlineStr">
+        <is>
+          <t>20-24 weeks</t>
+        </is>
+      </c>
+      <c r="O47" s="78" t="inlineStr">
+        <is>
+          <t>ACL Findings / PNAS Nexus (Q1)</t>
+        </is>
+      </c>
+      <c r="P47" s="79" t="inlineStr">
+        <is>
+          <t>Hot topic — Urdu misinformation is real problem; high impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="B48" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" s="84" t="inlineStr">
+        <is>
+          <t>No — needs medical annotators</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Biomedical NER + Text Mining</t>
+        </is>
+      </c>
+      <c r="E48" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F48" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G48" s="70" t="inlineStr">
+        <is>
+          <t>400-500 hrs</t>
+        </is>
+      </c>
+      <c r="H48" s="55" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I48" s="70" t="inlineStr">
+        <is>
+          <t>100-200</t>
+        </is>
+      </c>
+      <c r="J48" s="71" t="inlineStr">
+        <is>
+          <t>Translate PubMed abstracts via NLLB-200 + scrape Urdu medical articles from WebMD Urdu, Mayoclinic Urdu, Sehat Kahani (https://sehatkahani.com)</t>
+        </is>
+      </c>
+      <c r="K48" s="54" t="inlineStr">
+        <is>
+          <t>Yes (biomedical NER)</t>
+        </is>
+      </c>
+      <c r="L48" s="49" t="inlineStr">
+        <is>
+          <t>2-3 medical students — Medical students</t>
+        </is>
+      </c>
+      <c r="M48" s="70" t="inlineStr">
+        <is>
+          <t>12-16 weeks</t>
+        </is>
+      </c>
+      <c r="N48" s="72" t="inlineStr">
+        <is>
+          <t>20-24 weeks</t>
+        </is>
+      </c>
+      <c r="O48" s="73" t="inlineStr">
+        <is>
+          <t>JBI (Q1) / JAMIA / IEEE JBHI</t>
+        </is>
+      </c>
+      <c r="P48" s="74" t="inlineStr">
+        <is>
+          <t>First Urdu biomedical NLP — guaranteed top medical informatics journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="n">
+        <v>38</v>
+      </c>
+      <c r="B49" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="83" t="inlineStr">
+        <is>
+          <t>No — heavy annotation</t>
+        </is>
+      </c>
+      <c r="D49" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Task-Oriented Dialogue (MultiWOZ-style)</t>
+        </is>
+      </c>
+      <c r="E49" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F49" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G49" s="75" t="inlineStr">
+        <is>
+          <t>400-500 hrs</t>
+        </is>
+      </c>
+      <c r="H49" s="52" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I49" s="75" t="inlineStr">
+        <is>
+          <t>300-500</t>
+        </is>
+      </c>
+      <c r="J49" s="76" t="inlineStr">
+        <is>
+          <t>Translate MultiWOZ (https://github.com/budzianowski/multiwoz) via LLM + heavy post-edit; OR build via Wizard-of-Oz experiments with Urdu speakers</t>
+        </is>
+      </c>
+      <c r="K49" s="52" t="inlineStr">
+        <is>
+          <t>Yes (dialogue state + intent + slot)</t>
+        </is>
+      </c>
+      <c r="L49" s="51" t="inlineStr">
+        <is>
+          <t>4-5 trained annotators — Trained NLP annotators</t>
+        </is>
+      </c>
+      <c r="M49" s="75" t="inlineStr">
+        <is>
+          <t>16-20 weeks</t>
+        </is>
+      </c>
+      <c r="N49" s="77" t="inlineStr">
+        <is>
+          <t>24-30 weeks</t>
+        </is>
+      </c>
+      <c r="O49" s="78" t="inlineStr">
+        <is>
+          <t>ACL Main / EMNLP Main (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P49" s="79" t="inlineStr">
+        <is>
+          <t>First Urdu TOD — guaranteed ACL acceptance</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="B50" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="84" t="inlineStr">
+        <is>
+          <t>No — requires MD annotators</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Medical QA (MedQA-Urdu)</t>
+        </is>
+      </c>
+      <c r="E50" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F50" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G50" s="70" t="inlineStr">
+        <is>
+          <t>400-600 hrs</t>
+        </is>
+      </c>
+      <c r="H50" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I50" s="70" t="inlineStr">
+        <is>
+          <t>500-1000 (LLM fine-tune)</t>
+        </is>
+      </c>
+      <c r="J50" s="71" t="inlineStr">
+        <is>
+          <t>Translate MedQA (https://github.com/jinjiego/MedQA) via GPT-4o + medical professional post-edit; supplement with Pakistan Medical &amp; Dental Council exam questions (PMDC); Urdu medical articles on Mayoclinic Urdu</t>
+        </is>
+      </c>
+      <c r="K50" s="54" t="inlineStr">
+        <is>
+          <t>Yes (medical QA verification)</t>
+        </is>
+      </c>
+      <c r="L50" s="49" t="inlineStr">
+        <is>
+          <t>2-3 MBBS doctors — Medical doctors</t>
+        </is>
+      </c>
+      <c r="M50" s="70" t="inlineStr">
+        <is>
+          <t>12-16 weeks</t>
+        </is>
+      </c>
+      <c r="N50" s="72" t="inlineStr">
+        <is>
+          <t>24-30 weeks</t>
+        </is>
+      </c>
+      <c r="O50" s="73" t="inlineStr">
+        <is>
+          <t>JAMIA (Q1 SCI) / JBI (Q1) / ACL Findings</t>
+        </is>
+      </c>
+      <c r="P50" s="74" t="inlineStr">
+        <is>
+          <t>First Urdu medical NLP — huge impact; JAMIA is top medical informatics journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="B51" s="85" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" s="83" t="inlineStr">
+        <is>
+          <t>No — requires legal expertise</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Legal Document Analysis (Legal-BERT-Urdu)</t>
+        </is>
+      </c>
+      <c r="E51" s="75" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F51" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G51" s="75" t="inlineStr">
+        <is>
+          <t>500-700 hrs</t>
+        </is>
+      </c>
+      <c r="H51" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I51" s="75" t="inlineStr">
+        <is>
+          <t>500-1000</t>
+        </is>
+      </c>
+      <c r="J51" s="76" t="inlineStr">
+        <is>
+          <t>Pakistan Supreme Court judgments (https://www.supremecourt.gov.pk); Lahore High Court judgments; India Supreme Court Urdu judgments (https://main.sci.gov.in); CLIC Pakistan (https://clic.org.pk)</t>
+        </is>
+      </c>
+      <c r="K51" s="52" t="inlineStr">
+        <is>
+          <t>Yes (legal NER, judgment outcome)</t>
+        </is>
+      </c>
+      <c r="L51" s="51" t="inlineStr">
+        <is>
+          <t>3-4 law students — Law students</t>
+        </is>
+      </c>
+      <c r="M51" s="75" t="inlineStr">
+        <is>
+          <t>16-20 weeks</t>
+        </is>
+      </c>
+      <c r="N51" s="77" t="inlineStr">
+        <is>
+          <t>32-40 weeks</t>
+        </is>
+      </c>
+      <c r="O51" s="78" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence and Law (Q1 SCI) / ACL Findings</t>
+        </is>
+      </c>
+      <c r="P51" s="79" t="inlineStr">
+        <is>
+          <t>First Urdu legal NLP — guaranteed AI&amp;Law journal; high social impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="B52" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" s="84" t="inlineStr">
+        <is>
+          <t>No — needs $100k+ compute</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Native LLM (UrduGPT-7B from scratch)</t>
+        </is>
+      </c>
+      <c r="E52" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F52" s="54" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="G52" s="70" t="inlineStr">
+        <is>
+          <t>1000+ hrs</t>
+        </is>
+      </c>
+      <c r="H52" s="54" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="I52" s="70" t="inlineStr">
+        <is>
+          <t>10,000+ A100 hrs</t>
+        </is>
+      </c>
+      <c r="J52" s="71" t="inlineStr">
+        <is>
+          <t>Makhzan + scrape Common Crawl Urdu (https://commoncrawl.org); Urdu Wikipedia full dump; Jang/Dawn archives; Urdu books from Rekhta.org</t>
+        </is>
+      </c>
+      <c r="K52" s="50" t="inlineStr">
+        <is>
+          <t>No (self-supervised pre-training)</t>
+        </is>
+      </c>
+      <c r="L52" s="49" t="inlineStr">
+        <is>
+          <t>0 — N/A</t>
+        </is>
+      </c>
+      <c r="M52" s="70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N52" s="72" t="inlineStr">
+        <is>
+          <t>20-30 weeks</t>
+        </is>
+      </c>
+      <c r="O52" s="73" t="inlineStr">
+        <is>
+          <t>ACL Main / NeurIPS (CCF-A top tier)</t>
+        </is>
+      </c>
+      <c r="P52" s="74" t="inlineStr">
+        <is>
+          <t>First native Urdu LLM = guaranteed top-venue; but needs big compute budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="n">
+        <v>42</v>
+      </c>
+      <c r="B53" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" s="83" t="inlineStr">
+        <is>
+          <t>No — needs physical data collection</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Nastaliq Handwritten OCR (50k+ images)</t>
+        </is>
+      </c>
+      <c r="E53" s="75" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F53" s="52" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="G53" s="75" t="inlineStr">
+        <is>
+          <t>600-800 hrs</t>
+        </is>
+      </c>
+      <c r="H53" s="52" t="inlineStr">
+        <is>
+          <t>Medium-High</t>
+        </is>
+      </c>
+      <c r="I53" s="75" t="inlineStr">
+        <is>
+          <t>300-600 (CRNN training)</t>
+        </is>
+      </c>
+      <c r="J53" s="76" t="inlineStr">
+        <is>
+          <t>Collect handwritten samples from universities in Pakistan (NUST, FAST, LUMS); partner with Urdu departments; scan historical manuscripts from Punjab Digital Library</t>
+        </is>
+      </c>
+      <c r="K53" s="52" t="inlineStr">
+        <is>
+          <t>Yes (line-level transcription)</t>
+        </is>
+      </c>
+      <c r="L53" s="51" t="inlineStr">
+        <is>
+          <t>5+ annotators — Urdu native readers</t>
+        </is>
+      </c>
+      <c r="M53" s="75" t="inlineStr">
+        <is>
+          <t>20-30 weeks</t>
+        </is>
+      </c>
+      <c r="N53" s="77" t="inlineStr">
+        <is>
+          <t>30-40 weeks</t>
+        </is>
+      </c>
+      <c r="O53" s="78" t="inlineStr">
+        <is>
+          <t>Pattern Recognition (Q1) / ICDAR (CCF-B)</t>
+        </is>
+      </c>
+      <c r="P53" s="79" t="inlineStr">
+        <is>
+          <t>First public Nastaliq handwritten corpus; ICDAR loves OCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="B54" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" s="84" t="inlineStr">
+        <is>
+          <t>No — massive undertaking</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>Urdu Knowledge Graph Construction (Urdu DBpedia)</t>
+        </is>
+      </c>
+      <c r="E54" s="70" t="inlineStr">
+        <is>
+          <t>Zero-work</t>
+        </is>
+      </c>
+      <c r="F54" s="54" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="G54" s="70" t="inlineStr">
+        <is>
+          <t>800+ hrs</t>
+        </is>
+      </c>
+      <c r="H54" s="54" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I54" s="70" t="inlineStr">
+        <is>
+          <t>500-1000</t>
+        </is>
+      </c>
+      <c r="J54" s="71" t="inlineStr">
+        <is>
+          <t>Urdu Wikipedia full dump (https://dumps.wikimedia.org/urwiki/); Wikidata Urdu entities (https://www.wikidata.org); use DBpedia extraction framework</t>
+        </is>
+      </c>
+      <c r="K54" s="54" t="inlineStr">
+        <is>
+          <t>Yes (relation triples verification)</t>
+        </is>
+      </c>
+      <c r="L54" s="49" t="inlineStr">
+        <is>
+          <t>5+ students — Students with ontology training</t>
+        </is>
+      </c>
+      <c r="M54" s="70" t="inlineStr">
+        <is>
+          <t>20+ weeks</t>
+        </is>
+      </c>
+      <c r="N54" s="72" t="inlineStr">
+        <is>
+          <t>30+ weeks</t>
+        </is>
+      </c>
+      <c r="O54" s="73" t="inlineStr">
+        <is>
+          <t>ISWC (CCF-C top semantic web venue) / KBS (Q1)</t>
+        </is>
+      </c>
+      <c r="P54" s="74" t="inlineStr">
+        <is>
+          <t>First Urdu KG — major undertaking but ISWC loves it</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="B55" s="86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" s="83" t="inlineStr">
+        <is>
+          <t>No — requires deaf community partnership</t>
+        </is>
+      </c>
+      <c r="D55" s="27" t="inlineStr">
+        <is>
+          <t>Urdu Sign Language Recognition (large-scale)</t>
+        </is>
+      </c>
+      <c r="E55" s="75" t="inlineStr">
+        <is>
+          <t>Tiny-dataset</t>
+        </is>
+      </c>
+      <c r="F55" s="52" t="inlineStr">
+        <is>
+          <t>Very High</t>
+        </is>
+      </c>
+      <c r="G55" s="75" t="inlineStr">
+        <is>
+          <t>800+ hrs</t>
+        </is>
+      </c>
+      <c r="H55" s="52" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I55" s="75" t="inlineStr">
+        <is>
+          <t>500-1000</t>
+        </is>
+      </c>
+      <c r="J55" s="76" t="inlineStr">
+        <is>
+          <t>Partner with Pakistan Association of the Deaf; record videos of native PSL signers; supplement with existing FSL archive</t>
+        </is>
+      </c>
+      <c r="K55" s="52" t="inlineStr">
+        <is>
+          <t>Yes (gloss + video)</t>
+        </is>
+      </c>
+      <c r="L55" s="51" t="inlineStr">
+        <is>
+          <t>5+ PSL experts + deaf community — PSL linguists + deaf community</t>
+        </is>
+      </c>
+      <c r="M55" s="75" t="inlineStr">
+        <is>
+          <t>20+ weeks</t>
+        </is>
+      </c>
+      <c r="N55" s="77" t="inlineStr">
+        <is>
+          <t>30+ weeks</t>
+        </is>
+      </c>
+      <c r="O55" s="78" t="inlineStr">
+        <is>
+          <t>CVPR / ECCV (CCF-A) / IEEE TPAMI</t>
+        </is>
+      </c>
+      <c r="P55" s="79" t="inlineStr">
+        <is>
+          <t>First large-scale Urdu sign language dataset — major social impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="58" t="inlineStr">
+        <is>
+          <t>TOP 5 EASY WINS — Do These First (highest ROI, lowest effort)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" s="87" t="inlineStr">
+        <is>
+          <t>ROI 9/10</t>
+        </is>
+      </c>
+      <c r="C59" s="88" t="inlineStr">
+        <is>
+          <t>Urdu Topic Modeling (Neural, large-scale)</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="n"/>
+      <c r="E59" s="14" t="n"/>
+      <c r="F59" s="14" t="n"/>
+      <c r="G59" s="14" t="n"/>
+      <c r="H59" s="14" t="n"/>
+      <c r="I59" s="89" t="inlineStr">
+        <is>
+          <t>Effort: Low (40-60 hrs)</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="n"/>
+      <c r="K59" s="14" t="n"/>
+      <c r="L59" s="89" t="inlineStr">
+        <is>
+          <t>Compute: Low (10-20)</t>
+        </is>
+      </c>
+      <c r="M59" s="14" t="n"/>
+      <c r="N59" s="14" t="n"/>
+      <c r="O59" s="90" t="inlineStr">
+        <is>
+          <t>Target: IEEE Access / PLOS ONE (Q1 SCI)</t>
+        </is>
+      </c>
+      <c r="P59" s="14" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="91" t="n">
+        <v>2</v>
+      </c>
+      <c r="B60" s="91" t="inlineStr">
+        <is>
+          <t>ROI 9/10</t>
+        </is>
+      </c>
+      <c r="C60" s="92" t="inlineStr">
+        <is>
+          <t>Translate DROP to Urdu (Numerical Reasoning)</t>
+        </is>
+      </c>
+      <c r="D60" s="93" t="n"/>
+      <c r="E60" s="93" t="n"/>
+      <c r="F60" s="93" t="n"/>
+      <c r="G60" s="93" t="n"/>
+      <c r="H60" s="93" t="n"/>
+      <c r="I60" s="94" t="inlineStr">
+        <is>
+          <t>Effort: Low (50-70 hrs)</t>
+        </is>
+      </c>
+      <c r="J60" s="93" t="n"/>
+      <c r="K60" s="93" t="n"/>
+      <c r="L60" s="94" t="inlineStr">
+        <is>
+          <t>Compute: Low (20-40 (fine-tune mT5))</t>
+        </is>
+      </c>
+      <c r="M60" s="93" t="n"/>
+      <c r="N60" s="93" t="n"/>
+      <c r="O60" s="95" t="inlineStr">
+        <is>
+          <t>Target: ACL Findings / EMNLP Findings (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P60" s="93" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" s="87" t="inlineStr">
+        <is>
+          <t>ROI 9/10</t>
+        </is>
+      </c>
+      <c r="C61" s="88" t="inlineStr">
+        <is>
+          <t>Urdu Document Clustering (large-scale)</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="n"/>
+      <c r="E61" s="14" t="n"/>
+      <c r="F61" s="14" t="n"/>
+      <c r="G61" s="14" t="n"/>
+      <c r="H61" s="14" t="n"/>
+      <c r="I61" s="89" t="inlineStr">
+        <is>
+          <t>Effort: Low (50-70 hrs)</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="n"/>
+      <c r="K61" s="14" t="n"/>
+      <c r="L61" s="89" t="inlineStr">
+        <is>
+          <t>Compute: Low (15-30)</t>
+        </is>
+      </c>
+      <c r="M61" s="14" t="n"/>
+      <c r="N61" s="14" t="n"/>
+      <c r="O61" s="90" t="inlineStr">
+        <is>
+          <t>Target: IEEE Access (Q1)</t>
+        </is>
+      </c>
+      <c r="P61" s="14" t="n"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="91" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" s="91" t="inlineStr">
+        <is>
+          <t>ROI 9/10</t>
+        </is>
+      </c>
+      <c r="C62" s="92" t="inlineStr">
+        <is>
+          <t>Urdu Document-to-Document Similarity (large-scale)</t>
+        </is>
+      </c>
+      <c r="D62" s="93" t="n"/>
+      <c r="E62" s="93" t="n"/>
+      <c r="F62" s="93" t="n"/>
+      <c r="G62" s="93" t="n"/>
+      <c r="H62" s="93" t="n"/>
+      <c r="I62" s="94" t="inlineStr">
+        <is>
+          <t>Effort: Low (50-70 hrs)</t>
+        </is>
+      </c>
+      <c r="J62" s="93" t="n"/>
+      <c r="K62" s="93" t="n"/>
+      <c r="L62" s="94" t="inlineStr">
+        <is>
+          <t>Compute: Low (15-30)</t>
+        </is>
+      </c>
+      <c r="M62" s="93" t="n"/>
+      <c r="N62" s="93" t="n"/>
+      <c r="O62" s="95" t="inlineStr">
+        <is>
+          <t>Target: IEEE Access (Q1)</t>
+        </is>
+      </c>
+      <c r="P62" s="93" t="n"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="B63" s="87" t="inlineStr">
+        <is>
+          <t>ROI 9/10</t>
+        </is>
+      </c>
+      <c r="C63" s="88" t="inlineStr">
+        <is>
+          <t>Translate COMET-ATOMIC to Urdu (Commonsense Reasoning)</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="n"/>
+      <c r="E63" s="14" t="n"/>
+      <c r="F63" s="14" t="n"/>
+      <c r="G63" s="14" t="n"/>
+      <c r="H63" s="14" t="n"/>
+      <c r="I63" s="89" t="inlineStr">
+        <is>
+          <t>Effort: Low (60-80 hrs)</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="n"/>
+      <c r="K63" s="14" t="n"/>
+      <c r="L63" s="89" t="inlineStr">
+        <is>
+          <t>Compute: Low (20-50 (A100 hrs for fine-tuning))</t>
+        </is>
+      </c>
+      <c r="M63" s="14" t="n"/>
+      <c r="N63" s="14" t="n"/>
+      <c r="O63" s="90" t="inlineStr">
+        <is>
+          <t>Target: ACL Findings / EMNLP Findings (CCF-A)</t>
+        </is>
+      </c>
+      <c r="P63" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A11:P55"/>
+  <mergeCells count="31">
+    <mergeCell ref="C63:H63"/>
+    <mergeCell ref="A5:P5"/>
+    <mergeCell ref="L62:N62"/>
+    <mergeCell ref="B8:P8"/>
+    <mergeCell ref="C59:H59"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="C60:H60"/>
+    <mergeCell ref="L63:N63"/>
+    <mergeCell ref="L60:N60"/>
+    <mergeCell ref="A58:P58"/>
+    <mergeCell ref="C61:H61"/>
+    <mergeCell ref="O63:P63"/>
+    <mergeCell ref="B9:P9"/>
+    <mergeCell ref="L59:N59"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="A3:N3"/>
+    <mergeCell ref="B6:P6"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="L61:N61"/>
+    <mergeCell ref="O62:P62"/>
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="B7:P7"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="C62:H62"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="A3:P3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>